--- a/data/nzd0509/nzd0509.xlsx
+++ b/data/nzd0509/nzd0509.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q449"/>
+  <dimension ref="A1:Q453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25983,6 +25983,234 @@
         <v>324.05</v>
       </c>
       <c r="Q449" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>387.6</v>
+      </c>
+      <c r="C450" t="n">
+        <v>330.43</v>
+      </c>
+      <c r="D450" t="n">
+        <v>325.28</v>
+      </c>
+      <c r="E450" t="n">
+        <v>334.6</v>
+      </c>
+      <c r="F450" t="n">
+        <v>331.49</v>
+      </c>
+      <c r="G450" t="n">
+        <v>332.83</v>
+      </c>
+      <c r="H450" t="n">
+        <v>336.04</v>
+      </c>
+      <c r="I450" t="n">
+        <v>326.47</v>
+      </c>
+      <c r="J450" t="n">
+        <v>327.02</v>
+      </c>
+      <c r="K450" t="n">
+        <v>323.01</v>
+      </c>
+      <c r="L450" t="n">
+        <v>325.49</v>
+      </c>
+      <c r="M450" t="n">
+        <v>332.21</v>
+      </c>
+      <c r="N450" t="n">
+        <v>339.58</v>
+      </c>
+      <c r="O450" t="n">
+        <v>331.13</v>
+      </c>
+      <c r="P450" t="n">
+        <v>323.84</v>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>384.79</v>
+      </c>
+      <c r="C451" t="n">
+        <v>327.09</v>
+      </c>
+      <c r="D451" t="n">
+        <v>321.19</v>
+      </c>
+      <c r="E451" t="n">
+        <v>328.41</v>
+      </c>
+      <c r="F451" t="n">
+        <v>325.76</v>
+      </c>
+      <c r="G451" t="n">
+        <v>328.26</v>
+      </c>
+      <c r="H451" t="n">
+        <v>332.75</v>
+      </c>
+      <c r="I451" t="n">
+        <v>318.88</v>
+      </c>
+      <c r="J451" t="n">
+        <v>320.97</v>
+      </c>
+      <c r="K451" t="n">
+        <v>317.51</v>
+      </c>
+      <c r="L451" t="n">
+        <v>320.57</v>
+      </c>
+      <c r="M451" t="n">
+        <v>327.14</v>
+      </c>
+      <c r="N451" t="n">
+        <v>334.34</v>
+      </c>
+      <c r="O451" t="n">
+        <v>328.83</v>
+      </c>
+      <c r="P451" t="n">
+        <v>321.3</v>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>384.87</v>
+      </c>
+      <c r="C452" t="n">
+        <v>325.41</v>
+      </c>
+      <c r="D452" t="n">
+        <v>318.95</v>
+      </c>
+      <c r="E452" t="n">
+        <v>326.44</v>
+      </c>
+      <c r="F452" t="n">
+        <v>324.14</v>
+      </c>
+      <c r="G452" t="n">
+        <v>325.61</v>
+      </c>
+      <c r="H452" t="n">
+        <v>331.19</v>
+      </c>
+      <c r="I452" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="J452" t="n">
+        <v>317.86</v>
+      </c>
+      <c r="K452" t="n">
+        <v>314.59</v>
+      </c>
+      <c r="L452" t="n">
+        <v>318.02</v>
+      </c>
+      <c r="M452" t="n">
+        <v>323.23</v>
+      </c>
+      <c r="N452" t="n">
+        <v>331.42</v>
+      </c>
+      <c r="O452" t="n">
+        <v>327.4</v>
+      </c>
+      <c r="P452" t="n">
+        <v>319.53</v>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>384</v>
+      </c>
+      <c r="C453" t="n">
+        <v>322.91</v>
+      </c>
+      <c r="D453" t="n">
+        <v>316.98</v>
+      </c>
+      <c r="E453" t="n">
+        <v>324.61</v>
+      </c>
+      <c r="F453" t="n">
+        <v>322.51</v>
+      </c>
+      <c r="G453" t="n">
+        <v>323.96</v>
+      </c>
+      <c r="H453" t="n">
+        <v>329.07</v>
+      </c>
+      <c r="I453" t="n">
+        <v>313.07</v>
+      </c>
+      <c r="J453" t="n">
+        <v>314.22</v>
+      </c>
+      <c r="K453" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="L453" t="n">
+        <v>315.69</v>
+      </c>
+      <c r="M453" t="n">
+        <v>319.68</v>
+      </c>
+      <c r="N453" t="n">
+        <v>327.12</v>
+      </c>
+      <c r="O453" t="n">
+        <v>324.29</v>
+      </c>
+      <c r="P453" t="n">
+        <v>316.66</v>
+      </c>
+      <c r="Q453" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25999,7 +26227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B525"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31252,6 +31480,66 @@
       </c>
       <c r="B525" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-07-02 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -31420,28 +31708,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2512647702640042</v>
+        <v>0.2463967690380636</v>
       </c>
       <c r="J2" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K2" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02840150537494435</v>
+        <v>0.02778201288653603</v>
       </c>
       <c r="M2" t="n">
-        <v>7.287225131533068</v>
+        <v>7.241411315471585</v>
       </c>
       <c r="N2" t="n">
-        <v>93.5791146888528</v>
+        <v>92.81220712569113</v>
       </c>
       <c r="O2" t="n">
-        <v>9.673629861063157</v>
+        <v>9.63390923383084</v>
       </c>
       <c r="P2" t="n">
-        <v>381.1594437756892</v>
+        <v>381.2227073073659</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31502,28 +31790,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1421638327715314</v>
+        <v>-0.1405575261488172</v>
       </c>
       <c r="J3" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K3" t="n">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006696057751297779</v>
+        <v>0.006656355388854118</v>
       </c>
       <c r="M3" t="n">
-        <v>9.146400447006595</v>
+        <v>9.085330607014056</v>
       </c>
       <c r="N3" t="n">
-        <v>129.7235151445117</v>
+        <v>128.6309466765568</v>
       </c>
       <c r="O3" t="n">
-        <v>11.3896231344374</v>
+        <v>11.34155838835902</v>
       </c>
       <c r="P3" t="n">
-        <v>329.4128544692054</v>
+        <v>329.3920614491446</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31580,28 +31868,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04574256685923943</v>
+        <v>0.04143901192244945</v>
       </c>
       <c r="J4" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K4" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007465696799621169</v>
+        <v>0.0006228172894058304</v>
       </c>
       <c r="M4" t="n">
-        <v>8.643185881289783</v>
+        <v>8.595653904968108</v>
       </c>
       <c r="N4" t="n">
-        <v>122.3153095396547</v>
+        <v>121.3590439052857</v>
       </c>
       <c r="O4" t="n">
-        <v>11.05962519887789</v>
+        <v>11.01630808870584</v>
       </c>
       <c r="P4" t="n">
-        <v>321.684051915605</v>
+        <v>321.739615175069</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31658,28 +31946,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2328721484926302</v>
+        <v>0.2255419917284604</v>
       </c>
       <c r="J5" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K5" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02298969293604658</v>
+        <v>0.02190699355600489</v>
       </c>
       <c r="M5" t="n">
-        <v>8.088468604770259</v>
+        <v>8.062894702448359</v>
       </c>
       <c r="N5" t="n">
-        <v>101.9348532771396</v>
+        <v>101.2939232296302</v>
       </c>
       <c r="O5" t="n">
-        <v>10.09627917983351</v>
+        <v>10.06448822492382</v>
       </c>
       <c r="P5" t="n">
-        <v>326.2435599635444</v>
+        <v>326.3375880498722</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31736,28 +32024,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3592668770547435</v>
+        <v>0.3471438791492135</v>
       </c>
       <c r="J6" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K6" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05912977646271145</v>
+        <v>0.05605140232851147</v>
       </c>
       <c r="M6" t="n">
-        <v>7.704493599812471</v>
+        <v>7.691776386747321</v>
       </c>
       <c r="N6" t="n">
-        <v>90.84049083905063</v>
+        <v>90.5132343225002</v>
       </c>
       <c r="O6" t="n">
-        <v>9.531027795523977</v>
+        <v>9.513844350340204</v>
       </c>
       <c r="P6" t="n">
-        <v>322.9177278925078</v>
+        <v>323.073165413193</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31814,28 +32102,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6417113596988446</v>
+        <v>0.6314602539073872</v>
       </c>
       <c r="J7" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K7" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1963890310978942</v>
+        <v>0.1932552307164749</v>
       </c>
       <c r="M7" t="n">
-        <v>6.91161439418255</v>
+        <v>6.90070728259411</v>
       </c>
       <c r="N7" t="n">
-        <v>74.52975790236471</v>
+        <v>74.23832027789979</v>
       </c>
       <c r="O7" t="n">
-        <v>8.633061907710653</v>
+        <v>8.616166216937774</v>
       </c>
       <c r="P7" t="n">
-        <v>315.9960755693813</v>
+        <v>316.1275241248811</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31892,28 +32180,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8304025146879581</v>
+        <v>0.8240667561926827</v>
       </c>
       <c r="J8" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K8" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2010621140626419</v>
+        <v>0.2011527738289598</v>
       </c>
       <c r="M8" t="n">
-        <v>8.641503965264636</v>
+        <v>8.602614961874931</v>
       </c>
       <c r="N8" t="n">
-        <v>120.8672725851618</v>
+        <v>119.9535996233764</v>
       </c>
       <c r="O8" t="n">
-        <v>10.99396528033274</v>
+        <v>10.95233306758776</v>
       </c>
       <c r="P8" t="n">
-        <v>313.3836375295828</v>
+        <v>313.465040455489</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31970,28 +32258,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3612091497225027</v>
+        <v>0.3518340191576071</v>
       </c>
       <c r="J9" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K9" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02318986256670119</v>
+        <v>0.02236103439274928</v>
       </c>
       <c r="M9" t="n">
-        <v>13.24888220378034</v>
+        <v>13.18133837752505</v>
       </c>
       <c r="N9" t="n">
-        <v>243.2943804660864</v>
+        <v>241.5848707944246</v>
       </c>
       <c r="O9" t="n">
-        <v>15.59789666801541</v>
+        <v>15.54300070110095</v>
       </c>
       <c r="P9" t="n">
-        <v>313.9466447077388</v>
+        <v>314.0668650510773</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32048,28 +32336,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06626288082114831</v>
+        <v>-0.07131012997073598</v>
       </c>
       <c r="J10" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K10" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L10" t="n">
-        <v>0.000839095916689514</v>
+        <v>0.0009874641899414449</v>
       </c>
       <c r="M10" t="n">
-        <v>12.16796409601822</v>
+        <v>12.10182681074818</v>
       </c>
       <c r="N10" t="n">
-        <v>229.1478543637625</v>
+        <v>227.371038714004</v>
       </c>
       <c r="O10" t="n">
-        <v>15.13763040782019</v>
+        <v>15.07882749798551</v>
       </c>
       <c r="P10" t="n">
-        <v>324.5158831161353</v>
+        <v>324.5809784825107</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32126,28 +32414,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1721350621283819</v>
+        <v>-0.1740909107646378</v>
       </c>
       <c r="J11" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K11" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004121423953025283</v>
+        <v>0.00428645444289466</v>
       </c>
       <c r="M11" t="n">
-        <v>14.86787568050451</v>
+        <v>14.76596818755343</v>
       </c>
       <c r="N11" t="n">
-        <v>312.7031355910814</v>
+        <v>310.0794545142589</v>
       </c>
       <c r="O11" t="n">
-        <v>17.68341413842591</v>
+        <v>17.60907307368161</v>
       </c>
       <c r="P11" t="n">
-        <v>322.4707999763409</v>
+        <v>322.4961180745426</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32204,28 +32492,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0199485747661517</v>
+        <v>-0.02569152307914658</v>
       </c>
       <c r="J12" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K12" t="n">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L12" t="n">
-        <v>7.805340897681923e-05</v>
+        <v>0.0001316007998286572</v>
       </c>
       <c r="M12" t="n">
-        <v>12.52687243604594</v>
+        <v>12.45095714471735</v>
       </c>
       <c r="N12" t="n">
-        <v>222.6549868202788</v>
+        <v>220.8760416568873</v>
       </c>
       <c r="O12" t="n">
-        <v>14.92162815581057</v>
+        <v>14.86189899228518</v>
       </c>
       <c r="P12" t="n">
-        <v>323.5662213444773</v>
+        <v>323.6403568886461</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32282,28 +32570,28 @@
         <v>0.1389</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3400343151940933</v>
+        <v>-0.3380267164042007</v>
       </c>
       <c r="J13" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K13" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03006009277102173</v>
+        <v>0.03018077734299685</v>
       </c>
       <c r="M13" t="n">
-        <v>9.684349474886973</v>
+        <v>9.634159916270468</v>
       </c>
       <c r="N13" t="n">
-        <v>165.1591406373012</v>
+        <v>163.8965760751516</v>
       </c>
       <c r="O13" t="n">
-        <v>12.85142562664941</v>
+        <v>12.80220981218288</v>
       </c>
       <c r="P13" t="n">
-        <v>333.5948034008582</v>
+        <v>333.5691975929572</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32360,28 +32648,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4527936124770882</v>
+        <v>-0.432717628875712</v>
       </c>
       <c r="J14" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K14" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05191859194476556</v>
+        <v>0.04807818828120169</v>
       </c>
       <c r="M14" t="n">
-        <v>10.15893778991624</v>
+        <v>10.18148347868383</v>
       </c>
       <c r="N14" t="n">
-        <v>165.7394589197733</v>
+        <v>165.4892632426997</v>
       </c>
       <c r="O14" t="n">
-        <v>12.87398380144131</v>
+        <v>12.86426302757759</v>
       </c>
       <c r="P14" t="n">
-        <v>334.3185025216989</v>
+        <v>334.0614367331575</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32438,28 +32726,28 @@
         <v>0.089</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2322617211666503</v>
+        <v>-0.2336809944758644</v>
       </c>
       <c r="J15" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K15" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02280871313124666</v>
+        <v>0.02345968491772055</v>
       </c>
       <c r="M15" t="n">
-        <v>7.869648511102038</v>
+        <v>7.817658579049609</v>
       </c>
       <c r="N15" t="n">
-        <v>102.314383537685</v>
+        <v>101.4663989884444</v>
       </c>
       <c r="O15" t="n">
-        <v>10.11505726813669</v>
+        <v>10.07305311156674</v>
       </c>
       <c r="P15" t="n">
-        <v>334.9216060537151</v>
+        <v>334.9398421066349</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32516,28 +32804,28 @@
         <v>0.035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.329492032008943</v>
+        <v>-0.3374507021418798</v>
       </c>
       <c r="J16" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="K16" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04585958326678052</v>
+        <v>0.04868259318530577</v>
       </c>
       <c r="M16" t="n">
-        <v>7.589998058593118</v>
+        <v>7.557958747289661</v>
       </c>
       <c r="N16" t="n">
-        <v>99.99415874592023</v>
+        <v>99.32987129383267</v>
       </c>
       <c r="O16" t="n">
-        <v>9.999707933030855</v>
+        <v>9.966437241754582</v>
       </c>
       <c r="P16" t="n">
-        <v>333.5237033938257</v>
+        <v>333.625713441369</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32575,7 +32863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q449"/>
+  <dimension ref="A1:Q453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71509,6 +71797,354 @@
         </is>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>-45.89907844715319,170.65228493592434</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>-45.89829771349555,170.65202399109884</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>-45.89788458367989,170.65134817529227</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>-45.897572507570146,170.65055217280917</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>-45.897261196360866,170.64977166668805</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>-45.89706524324276,170.64891072736228</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>-45.89688619043335,170.6480482014245</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>-45.89659745876697,170.64723117345656</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>-45.89648594531568,170.6463341615741</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>-45.89636069579064,170.64545028968595</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>-45.89629324773894,170.64455600161477</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>-45.89626343586678,170.64365295160093</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>-45.896236952126884,170.6427486287251</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>-45.89603721839937,170.64189242309504</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>-45.89584795385409,170.64103302549762</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>-45.899058589966565,170.6523073464351</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>-45.89827411100303,170.65205062812728</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>-45.89785568135445,170.65138079366193</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>-45.8975260362868,170.65059612686628</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>-45.897214278241904,170.64980225986622</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>-45.897026711917015,170.64893127451566</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-45.89685845133546,170.6480629938203</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-45.89653185373187,170.64725830748648</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>-45.896432440454596,170.64634847902332</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>-45.896311876455286,170.64546185320745</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>-45.89624957669292,170.64456634617446</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>-45.896218446349316,170.64366372306344</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>-45.896190700198794,170.6427616960359</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>-45.8960170343254,170.6418989531435</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>-45.895825663658066,170.64104023714515</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:15+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>-45.89905915529579,170.65230670841365</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>-45.89826223908807,170.65206402638444</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>-45.89783985220372,170.65139865798685</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>-45.897511246552945,170.65061011546018</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>-45.89720101343167,170.6498109092369</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>-45.89700436880483,170.6489431891535</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-45.896845298449335,170.64807000783853</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-45.896505231396404,170.64726931837814</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>-45.896404936301785,170.64635583889068</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>-45.896285957825526,170.64546799237718</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>-45.89622694230869,170.64457170767713</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>-45.89618375029032,170.64367203003647</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>-45.89616492622261,170.6427689778097</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>-45.89600448509653,170.64190301312763</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>-45.89581013072581,170.64104526258095</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>-45.89905300734029,170.65231364689606</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>-45.8982445725448,170.65208396425655</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>-45.897825931028464,170.65141436901413</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>-45.8974975078645,170.65062310993403</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>-45.89718766673913,170.64981961199445</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>-45.89699045705499,170.6489506076966</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-45.8968274240135,170.64807953970396</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-45.89648163432518,170.6472790780229</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>-45.89637274494513,170.6463644530021</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>-45.896263855979875,170.64547322748624</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>-45.896206260694505,170.64457660661466</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>-45.89615224875252,170.64367957216342</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>-45.896126971393414,170.64277970095665</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>-45.895977192716956,170.64191184287662</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>-45.89578494455817,170.64105341116266</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0509/nzd0509.xlsx
+++ b/data/nzd0509/nzd0509.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q453"/>
+  <dimension ref="A1:Q456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26211,6 +26211,177 @@
         <v>316.66</v>
       </c>
       <c r="Q453" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>383.34</v>
+      </c>
+      <c r="C454" t="n">
+        <v>322.91</v>
+      </c>
+      <c r="D454" t="n">
+        <v>316.98</v>
+      </c>
+      <c r="E454" t="n">
+        <v>324.61</v>
+      </c>
+      <c r="F454" t="n">
+        <v>322.51</v>
+      </c>
+      <c r="G454" t="n">
+        <v>323.96</v>
+      </c>
+      <c r="H454" t="n">
+        <v>329.07</v>
+      </c>
+      <c r="I454" t="n">
+        <v>313.07</v>
+      </c>
+      <c r="J454" t="n">
+        <v>314.22</v>
+      </c>
+      <c r="K454" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="L454" t="n">
+        <v>315.69</v>
+      </c>
+      <c r="M454" t="n">
+        <v>319.68</v>
+      </c>
+      <c r="N454" t="n">
+        <v>327.12</v>
+      </c>
+      <c r="O454" t="n">
+        <v>324.29</v>
+      </c>
+      <c r="P454" t="n">
+        <v>316.66</v>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>383.24</v>
+      </c>
+      <c r="C455" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="D455" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="E455" t="n">
+        <v>322.22</v>
+      </c>
+      <c r="F455" t="n">
+        <v>319.89</v>
+      </c>
+      <c r="G455" t="n">
+        <v>321.06</v>
+      </c>
+      <c r="H455" t="n">
+        <v>326.46</v>
+      </c>
+      <c r="I455" t="n">
+        <v>309.83</v>
+      </c>
+      <c r="J455" t="n">
+        <v>311.11</v>
+      </c>
+      <c r="K455" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="L455" t="n">
+        <v>313.27</v>
+      </c>
+      <c r="M455" t="n">
+        <v>316.47</v>
+      </c>
+      <c r="N455" t="n">
+        <v>324.36</v>
+      </c>
+      <c r="O455" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="P455" t="n">
+        <v>314.87</v>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:40+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>383.24</v>
+      </c>
+      <c r="C456" t="n">
+        <v>321.05</v>
+      </c>
+      <c r="D456" t="n">
+        <v>314.5</v>
+      </c>
+      <c r="E456" t="n">
+        <v>319.82</v>
+      </c>
+      <c r="F456" t="n">
+        <v>318.58</v>
+      </c>
+      <c r="G456" t="n">
+        <v>318.41</v>
+      </c>
+      <c r="H456" t="n">
+        <v>326.46</v>
+      </c>
+      <c r="I456" t="n">
+        <v>309.83</v>
+      </c>
+      <c r="J456" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="K456" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="L456" t="n">
+        <v>313.27</v>
+      </c>
+      <c r="M456" t="n">
+        <v>316.47</v>
+      </c>
+      <c r="N456" t="n">
+        <v>324.36</v>
+      </c>
+      <c r="O456" t="n">
+        <v>322.7</v>
+      </c>
+      <c r="P456" t="n">
+        <v>314.87</v>
+      </c>
+      <c r="Q456" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26227,7 +26398,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B531"/>
+  <dimension ref="A1:B534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31540,6 +31711,36 @@
       </c>
       <c r="B531" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>-0.52</v>
       </c>
     </row>
   </sheetData>
@@ -31708,28 +31909,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2463967690380636</v>
+        <v>0.2400081045398944</v>
       </c>
       <c r="J2" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K2" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02778201288653603</v>
+        <v>0.02669013582659496</v>
       </c>
       <c r="M2" t="n">
-        <v>7.241411315471585</v>
+        <v>7.218606413242253</v>
       </c>
       <c r="N2" t="n">
-        <v>92.81220712569113</v>
+        <v>92.32824688224768</v>
       </c>
       <c r="O2" t="n">
-        <v>9.63390923383084</v>
+        <v>9.608758862738084</v>
       </c>
       <c r="P2" t="n">
-        <v>381.2227073073659</v>
+        <v>381.3060253215569</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31790,28 +31991,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1405575261488172</v>
+        <v>-0.1460330175611253</v>
       </c>
       <c r="J3" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K3" t="n">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006656355388854118</v>
+        <v>0.007267576417124944</v>
       </c>
       <c r="M3" t="n">
-        <v>9.085330607014056</v>
+        <v>9.049084582366257</v>
       </c>
       <c r="N3" t="n">
-        <v>128.6309466765568</v>
+        <v>127.8761619761955</v>
       </c>
       <c r="O3" t="n">
-        <v>11.34155838835902</v>
+        <v>11.30823425545277</v>
       </c>
       <c r="P3" t="n">
-        <v>329.3920614491446</v>
+        <v>329.4634715457299</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31868,28 +32069,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04143901192244945</v>
+        <v>0.03105273193168442</v>
       </c>
       <c r="J4" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K4" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006228172894058304</v>
+        <v>0.0003532616280643719</v>
       </c>
       <c r="M4" t="n">
-        <v>8.595653904968108</v>
+        <v>8.583789426431117</v>
       </c>
       <c r="N4" t="n">
-        <v>121.3590439052857</v>
+        <v>120.9327566510221</v>
       </c>
       <c r="O4" t="n">
-        <v>11.01630808870584</v>
+        <v>10.99694305936982</v>
       </c>
       <c r="P4" t="n">
-        <v>321.739615175069</v>
+        <v>321.8740868530675</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31946,28 +32147,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2255419917284604</v>
+        <v>0.2116159898053113</v>
       </c>
       <c r="J5" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K5" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02190699355600489</v>
+        <v>0.01944745716010121</v>
       </c>
       <c r="M5" t="n">
-        <v>8.062894702448359</v>
+        <v>8.0794285736654</v>
       </c>
       <c r="N5" t="n">
-        <v>101.2939232296302</v>
+        <v>101.3248324247457</v>
       </c>
       <c r="O5" t="n">
-        <v>10.06448822492382</v>
+        <v>10.06602366502015</v>
       </c>
       <c r="P5" t="n">
-        <v>326.3375880498722</v>
+        <v>326.5168062948229</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32024,28 +32225,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3471438791492135</v>
+        <v>0.3306158327844847</v>
       </c>
       <c r="J6" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K6" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05605140232851147</v>
+        <v>0.05120851259007708</v>
       </c>
       <c r="M6" t="n">
-        <v>7.691776386747321</v>
+        <v>7.717502001934041</v>
       </c>
       <c r="N6" t="n">
-        <v>90.5132343225002</v>
+        <v>90.88386760898452</v>
       </c>
       <c r="O6" t="n">
-        <v>9.513844350340204</v>
+        <v>9.533303079677291</v>
       </c>
       <c r="P6" t="n">
-        <v>323.073165413193</v>
+        <v>323.2858577247434</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32102,28 +32303,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6314602539073872</v>
+        <v>0.615061999721443</v>
       </c>
       <c r="J7" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K7" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1932552307164749</v>
+        <v>0.1851424799634281</v>
       </c>
       <c r="M7" t="n">
-        <v>6.90070728259411</v>
+        <v>6.937944480731576</v>
       </c>
       <c r="N7" t="n">
-        <v>74.23832027789979</v>
+        <v>74.71783511066995</v>
       </c>
       <c r="O7" t="n">
-        <v>8.616166216937774</v>
+        <v>8.643947889169043</v>
       </c>
       <c r="P7" t="n">
-        <v>316.1275241248811</v>
+        <v>316.33855824538</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32180,28 +32381,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8240667561926827</v>
+        <v>0.812621539794529</v>
       </c>
       <c r="J8" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K8" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2011527738289598</v>
+        <v>0.1981067419850334</v>
       </c>
       <c r="M8" t="n">
-        <v>8.602614961874931</v>
+        <v>8.610965462773711</v>
       </c>
       <c r="N8" t="n">
-        <v>119.9535996233764</v>
+        <v>119.6242024499863</v>
       </c>
       <c r="O8" t="n">
-        <v>10.95233306758776</v>
+        <v>10.93728496702844</v>
       </c>
       <c r="P8" t="n">
-        <v>313.465040455489</v>
+        <v>313.6125968275553</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32258,28 +32459,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3518340191576071</v>
+        <v>0.3345883243742231</v>
       </c>
       <c r="J9" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K9" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02236103439274928</v>
+        <v>0.02043375688488169</v>
       </c>
       <c r="M9" t="n">
-        <v>13.18133837752505</v>
+        <v>13.16257168976593</v>
       </c>
       <c r="N9" t="n">
-        <v>241.5848707944246</v>
+        <v>241.0409529991458</v>
       </c>
       <c r="O9" t="n">
-        <v>15.54300070110095</v>
+        <v>15.52549364751877</v>
       </c>
       <c r="P9" t="n">
-        <v>314.0668650510773</v>
+        <v>314.2887064809727</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32336,28 +32537,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.07131012997073598</v>
+        <v>-0.08828114465448494</v>
       </c>
       <c r="J10" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K10" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0009874641899414449</v>
+        <v>0.001524918306388567</v>
       </c>
       <c r="M10" t="n">
-        <v>12.10182681074818</v>
+        <v>12.10019585098341</v>
       </c>
       <c r="N10" t="n">
-        <v>227.371038714004</v>
+        <v>226.9372560167168</v>
       </c>
       <c r="O10" t="n">
-        <v>15.07882749798551</v>
+        <v>15.06443679719613</v>
       </c>
       <c r="P10" t="n">
-        <v>324.5809784825107</v>
+        <v>324.800415755477</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32414,28 +32615,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1740909107646378</v>
+        <v>-0.184067099389435</v>
       </c>
       <c r="J11" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K11" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00428645444289466</v>
+        <v>0.004845737578435094</v>
       </c>
       <c r="M11" t="n">
-        <v>14.76596818755343</v>
+        <v>14.70534723960556</v>
       </c>
       <c r="N11" t="n">
-        <v>310.0794545142589</v>
+        <v>308.3735288139237</v>
       </c>
       <c r="O11" t="n">
-        <v>17.60907307368161</v>
+        <v>17.56056743997539</v>
       </c>
       <c r="P11" t="n">
-        <v>322.4961180745426</v>
+        <v>322.6252794650979</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32492,28 +32693,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.02569152307914658</v>
+        <v>-0.03791948007635884</v>
       </c>
       <c r="J12" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K12" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0001316007998286572</v>
+        <v>0.0002896700661145779</v>
       </c>
       <c r="M12" t="n">
-        <v>12.45095714471735</v>
+        <v>12.42018205887464</v>
       </c>
       <c r="N12" t="n">
-        <v>220.8760416568873</v>
+        <v>219.932568538525</v>
       </c>
       <c r="O12" t="n">
-        <v>14.86189899228518</v>
+        <v>14.83012368588088</v>
       </c>
       <c r="P12" t="n">
-        <v>323.6403568886461</v>
+        <v>323.7986684822594</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32570,28 +32771,28 @@
         <v>0.1389</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3380267164042007</v>
+        <v>-0.3474560326950169</v>
       </c>
       <c r="J13" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K13" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03018077734299685</v>
+        <v>0.03216823542935454</v>
       </c>
       <c r="M13" t="n">
-        <v>9.634159916270468</v>
+        <v>9.618482113759461</v>
       </c>
       <c r="N13" t="n">
-        <v>163.8965760751516</v>
+        <v>163.1383364540011</v>
       </c>
       <c r="O13" t="n">
-        <v>12.80220981218288</v>
+        <v>12.77256185947052</v>
       </c>
       <c r="P13" t="n">
-        <v>333.5691975929572</v>
+        <v>333.6905046131511</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32648,28 +32849,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.432717628875712</v>
+        <v>-0.4287842659257428</v>
       </c>
       <c r="J14" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K14" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04807818828120169</v>
+        <v>0.0478103774391212</v>
       </c>
       <c r="M14" t="n">
-        <v>10.18148347868383</v>
+        <v>10.13599561586012</v>
       </c>
       <c r="N14" t="n">
-        <v>165.4892632426997</v>
+        <v>164.4608901117735</v>
       </c>
       <c r="O14" t="n">
-        <v>12.86426302757759</v>
+        <v>12.82423058556627</v>
       </c>
       <c r="P14" t="n">
-        <v>334.0614367331575</v>
+        <v>334.0108698352507</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32726,28 +32927,28 @@
         <v>0.089</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2336809944758644</v>
+        <v>-0.24105291421048</v>
       </c>
       <c r="J15" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K15" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02345968491772055</v>
+        <v>0.0251914842015899</v>
       </c>
       <c r="M15" t="n">
-        <v>7.817658579049609</v>
+        <v>7.798586321355165</v>
       </c>
       <c r="N15" t="n">
-        <v>101.4663989884444</v>
+        <v>100.9889867384649</v>
       </c>
       <c r="O15" t="n">
-        <v>10.07305311156674</v>
+        <v>10.04932767594255</v>
       </c>
       <c r="P15" t="n">
-        <v>334.9398421066349</v>
+        <v>335.0346729352511</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32804,28 +33005,28 @@
         <v>0.035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3374507021418798</v>
+        <v>-0.3497933717828401</v>
       </c>
       <c r="J16" t="n">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K16" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L16" t="n">
-        <v>0.04868259318530577</v>
+        <v>0.05248560106069156</v>
       </c>
       <c r="M16" t="n">
-        <v>7.557958747289661</v>
+        <v>7.562616765861063</v>
       </c>
       <c r="N16" t="n">
-        <v>99.32987129383267</v>
+        <v>99.20932122645861</v>
       </c>
       <c r="O16" t="n">
-        <v>9.966437241754582</v>
+        <v>9.960387604227991</v>
       </c>
       <c r="P16" t="n">
-        <v>333.625713441369</v>
+        <v>333.7844795214478</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32863,7 +33064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q453"/>
+  <dimension ref="A1:Q456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72145,6 +72346,267 @@
         </is>
       </c>
     </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>-45.89904834337375,170.65231891057135</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>-45.8982445725448,170.65208396425655</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>-45.897825931028464,170.65141436901413</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>-45.8974975078645,170.65062310993403</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>-45.89718766673913,170.64981961199445</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>-45.89699045705499,170.6489506076966</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>-45.8968274240135,170.64807953970396</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-45.89648163432518,170.6472790780229</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>-45.89637274494513,170.6463644530021</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>-45.896263855979875,170.64547322748624</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-45.896206260694505,170.64457660661466</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>-45.89615224875252,170.64367957216342</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>-45.896126971393414,170.64277970095665</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>-45.895977192716956,170.64191184287662</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>-45.89578494455817,170.64105341116266</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:32+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>-45.89904763671213,170.65231970809782</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>-45.89823142863416,170.6520987980251</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>-45.8978084058908,170.65143414735195</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>-45.89747956498475,170.65064008084917</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>-45.89716621377156,170.64983360046693</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>-45.89696600609929,170.64896364633884</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-45.89680541822089,170.64809127468055</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-45.896453629008455,170.64729066088682</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>-45.896345240790694,170.64637181285258</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>-45.896243440620076,170.64547806312513</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>-45.89618478021933,170.6445816947774</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>-45.89612376426269,170.64368639193785</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>-45.896102609688285,170.64278658371254</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>-45.89596323937783,170.64191635711774</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>-45.89576923611173,170.64105849337517</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:40+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>-45.89904763671213,170.65231970809782</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>-45.89823142863416,170.6520987980251</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>-45.8978084058908,170.65143414735195</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>-45.89746154702742,170.65065712276117</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>-45.89715548728704,170.64984059469907</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>-45.89694366298302,170.64897556094988</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-45.89680541822089,170.64809127468055</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-45.896453629008455,170.64729066088682</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>-45.89629677687695,170.6463847813161</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>-45.896243440620076,170.64547806312513</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>-45.89618478021933,170.6445816947774</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>-45.89612376426269,170.64368639193785</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>-45.896102609688285,170.64278658371254</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>-45.89596323937783,170.64191635711774</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>-45.89576923611173,170.64105849337517</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0509/nzd0509.xlsx
+++ b/data/nzd0509/nzd0509.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q456"/>
+  <dimension ref="A1:Q460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26382,6 +26382,234 @@
         <v>314.87</v>
       </c>
       <c r="Q456" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>382.67</v>
+      </c>
+      <c r="C457" t="n">
+        <v>323.49</v>
+      </c>
+      <c r="D457" t="n">
+        <v>315.99</v>
+      </c>
+      <c r="E457" t="n">
+        <v>319.77</v>
+      </c>
+      <c r="F457" t="n">
+        <v>318.73</v>
+      </c>
+      <c r="G457" t="n">
+        <v>318.72</v>
+      </c>
+      <c r="H457" t="n">
+        <v>327.17</v>
+      </c>
+      <c r="I457" t="n">
+        <v>312.54</v>
+      </c>
+      <c r="J457" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="K457" t="n">
+        <v>311.8</v>
+      </c>
+      <c r="L457" t="n">
+        <v>314.98</v>
+      </c>
+      <c r="M457" t="n">
+        <v>316.99</v>
+      </c>
+      <c r="N457" t="n">
+        <v>323.42</v>
+      </c>
+      <c r="O457" t="n">
+        <v>322.45</v>
+      </c>
+      <c r="P457" t="n">
+        <v>314.77</v>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>383.17</v>
+      </c>
+      <c r="C458" t="n">
+        <v>322.51</v>
+      </c>
+      <c r="D458" t="n">
+        <v>315.26</v>
+      </c>
+      <c r="E458" t="n">
+        <v>318.85</v>
+      </c>
+      <c r="F458" t="n">
+        <v>318.24</v>
+      </c>
+      <c r="G458" t="n">
+        <v>318.28</v>
+      </c>
+      <c r="H458" t="n">
+        <v>326.61</v>
+      </c>
+      <c r="I458" t="n">
+        <v>312.44</v>
+      </c>
+      <c r="J458" t="n">
+        <v>305.59</v>
+      </c>
+      <c r="K458" t="n">
+        <v>311.3</v>
+      </c>
+      <c r="L458" t="n">
+        <v>314.59</v>
+      </c>
+      <c r="M458" t="n">
+        <v>314.95</v>
+      </c>
+      <c r="N458" t="n">
+        <v>321.09</v>
+      </c>
+      <c r="O458" t="n">
+        <v>321.58</v>
+      </c>
+      <c r="P458" t="n">
+        <v>315.18</v>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>382.68</v>
+      </c>
+      <c r="C459" t="n">
+        <v>321.88</v>
+      </c>
+      <c r="D459" t="n">
+        <v>314.51</v>
+      </c>
+      <c r="E459" t="n">
+        <v>318.26</v>
+      </c>
+      <c r="F459" t="n">
+        <v>317.96</v>
+      </c>
+      <c r="G459" t="n">
+        <v>317.77</v>
+      </c>
+      <c r="H459" t="n">
+        <v>326.22</v>
+      </c>
+      <c r="I459" t="n">
+        <v>312.25</v>
+      </c>
+      <c r="J459" t="n">
+        <v>305.34</v>
+      </c>
+      <c r="K459" t="n">
+        <v>310.67</v>
+      </c>
+      <c r="L459" t="n">
+        <v>314.19</v>
+      </c>
+      <c r="M459" t="n">
+        <v>313.35</v>
+      </c>
+      <c r="N459" t="n">
+        <v>318.83</v>
+      </c>
+      <c r="O459" t="n">
+        <v>320.55</v>
+      </c>
+      <c r="P459" t="n">
+        <v>314.62</v>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>382.68</v>
+      </c>
+      <c r="C460" t="n">
+        <v>322.13</v>
+      </c>
+      <c r="D460" t="n">
+        <v>314.78</v>
+      </c>
+      <c r="E460" t="n">
+        <v>318.44</v>
+      </c>
+      <c r="F460" t="n">
+        <v>318.02</v>
+      </c>
+      <c r="G460" t="n">
+        <v>317.87</v>
+      </c>
+      <c r="H460" t="n">
+        <v>326.03</v>
+      </c>
+      <c r="I460" t="n">
+        <v>312.19</v>
+      </c>
+      <c r="J460" t="n">
+        <v>305.75</v>
+      </c>
+      <c r="K460" t="n">
+        <v>310.59</v>
+      </c>
+      <c r="L460" t="n">
+        <v>313.62</v>
+      </c>
+      <c r="M460" t="n">
+        <v>312.5</v>
+      </c>
+      <c r="N460" t="n">
+        <v>316.6</v>
+      </c>
+      <c r="O460" t="n">
+        <v>318.94</v>
+      </c>
+      <c r="P460" t="n">
+        <v>312.65</v>
+      </c>
+      <c r="Q460" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26398,7 +26626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B534"/>
+  <dimension ref="A1:B538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31741,6 +31969,46 @@
       </c>
       <c r="B534" t="n">
         <v>-0.52</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -31909,28 +32177,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2400081045398944</v>
+        <v>0.2309010301984259</v>
       </c>
       <c r="J2" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K2" t="n">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02669013582659496</v>
+        <v>0.02510474397145213</v>
       </c>
       <c r="M2" t="n">
-        <v>7.218606413242253</v>
+        <v>7.191454283582408</v>
       </c>
       <c r="N2" t="n">
-        <v>92.32824688224768</v>
+        <v>91.72580864152607</v>
       </c>
       <c r="O2" t="n">
-        <v>9.608758862738084</v>
+        <v>9.577359168451713</v>
       </c>
       <c r="P2" t="n">
-        <v>381.3060253215569</v>
+        <v>381.4251533270898</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31991,28 +32259,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1460330175611253</v>
+        <v>-0.1515276658865977</v>
       </c>
       <c r="J3" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K3" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007267576417124944</v>
+        <v>0.007947685717582864</v>
       </c>
       <c r="M3" t="n">
-        <v>9.049084582366257</v>
+        <v>8.993519736019632</v>
       </c>
       <c r="N3" t="n">
-        <v>127.8761619761955</v>
+        <v>126.8259737497682</v>
       </c>
       <c r="O3" t="n">
-        <v>11.30823425545277</v>
+        <v>11.2617038564228</v>
       </c>
       <c r="P3" t="n">
-        <v>329.4634715457299</v>
+        <v>329.5353459810347</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32069,28 +32337,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03105273193168442</v>
+        <v>0.01736138281422212</v>
       </c>
       <c r="J4" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K4" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003532616280643719</v>
+        <v>0.0001118774650530341</v>
       </c>
       <c r="M4" t="n">
-        <v>8.583789426431117</v>
+        <v>8.568933715677284</v>
       </c>
       <c r="N4" t="n">
-        <v>120.9327566510221</v>
+        <v>120.3672365868251</v>
       </c>
       <c r="O4" t="n">
-        <v>10.99694305936982</v>
+        <v>10.97120032570844</v>
       </c>
       <c r="P4" t="n">
-        <v>321.8740868530675</v>
+        <v>322.0518634009745</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32147,28 +32415,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2116159898053113</v>
+        <v>0.1876440119141573</v>
       </c>
       <c r="J5" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K5" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01944745716010121</v>
+        <v>0.01537994269126775</v>
       </c>
       <c r="M5" t="n">
-        <v>8.0794285736654</v>
+        <v>8.128115101825729</v>
       </c>
       <c r="N5" t="n">
-        <v>101.3248324247457</v>
+        <v>101.9745962996626</v>
       </c>
       <c r="O5" t="n">
-        <v>10.06602366502015</v>
+        <v>10.09824718947118</v>
       </c>
       <c r="P5" t="n">
-        <v>326.5168062948229</v>
+        <v>326.8261867395275</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32225,28 +32493,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3306158327844847</v>
+        <v>0.305613758763084</v>
       </c>
       <c r="J6" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K6" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05120851259007708</v>
+        <v>0.04402120308111745</v>
       </c>
       <c r="M6" t="n">
-        <v>7.717502001934041</v>
+        <v>7.768131137757806</v>
       </c>
       <c r="N6" t="n">
-        <v>90.88386760898452</v>
+        <v>91.75733070673762</v>
       </c>
       <c r="O6" t="n">
-        <v>9.533303079677291</v>
+        <v>9.579004682467673</v>
       </c>
       <c r="P6" t="n">
-        <v>323.2858577247434</v>
+        <v>323.6085239898224</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32303,28 +32571,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.615061999721443</v>
+        <v>0.5885862730200144</v>
       </c>
       <c r="J7" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K7" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1851424799634281</v>
+        <v>0.1710798193307079</v>
       </c>
       <c r="M7" t="n">
-        <v>6.937944480731576</v>
+        <v>7.015422414968366</v>
       </c>
       <c r="N7" t="n">
-        <v>74.71783511066995</v>
+        <v>75.93514080023458</v>
       </c>
       <c r="O7" t="n">
-        <v>8.643947889169043</v>
+        <v>8.714077162857498</v>
       </c>
       <c r="P7" t="n">
-        <v>316.33855824538</v>
+        <v>316.680245288525</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32381,28 +32649,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.812621539794529</v>
+        <v>0.7963408229392253</v>
       </c>
       <c r="J8" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K8" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1981067419850334</v>
+        <v>0.1934486772599155</v>
       </c>
       <c r="M8" t="n">
-        <v>8.610965462773711</v>
+        <v>8.62811020506228</v>
       </c>
       <c r="N8" t="n">
-        <v>119.6242024499863</v>
+        <v>119.283384295251</v>
       </c>
       <c r="O8" t="n">
-        <v>10.93728496702844</v>
+        <v>10.92169328882893</v>
       </c>
       <c r="P8" t="n">
-        <v>313.6125968275553</v>
+        <v>313.8231053971923</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -32459,28 +32727,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3345883243742231</v>
+        <v>0.3149721677486797</v>
       </c>
       <c r="J9" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K9" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02043375688488169</v>
+        <v>0.01837477907128582</v>
       </c>
       <c r="M9" t="n">
-        <v>13.16257168976593</v>
+        <v>13.12513871215977</v>
       </c>
       <c r="N9" t="n">
-        <v>241.0409529991458</v>
+        <v>239.9633106592106</v>
       </c>
       <c r="O9" t="n">
-        <v>15.52549364751877</v>
+        <v>15.49074919618837</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2887064809727</v>
+        <v>314.5417708383277</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -32537,28 +32805,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.08828114465448494</v>
+        <v>-0.1185933727532284</v>
       </c>
       <c r="J10" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K10" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001524918306388567</v>
+        <v>0.002765573609021632</v>
       </c>
       <c r="M10" t="n">
-        <v>12.10019585098341</v>
+        <v>12.13398731367058</v>
       </c>
       <c r="N10" t="n">
-        <v>226.9372560167168</v>
+        <v>227.3689674996154</v>
       </c>
       <c r="O10" t="n">
-        <v>15.06443679719613</v>
+        <v>15.07875881827199</v>
       </c>
       <c r="P10" t="n">
-        <v>324.800415755477</v>
+        <v>325.1934073592815</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32615,28 +32883,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.184067099389435</v>
+        <v>-0.195910245978117</v>
       </c>
       <c r="J11" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K11" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004845737578435094</v>
+        <v>0.005572314010153567</v>
       </c>
       <c r="M11" t="n">
-        <v>14.70534723960556</v>
+        <v>14.6199555499828</v>
       </c>
       <c r="N11" t="n">
-        <v>308.3735288139237</v>
+        <v>306.043243856585</v>
       </c>
       <c r="O11" t="n">
-        <v>17.56056743997539</v>
+        <v>17.49409168423971</v>
       </c>
       <c r="P11" t="n">
-        <v>322.6252794650979</v>
+        <v>322.7790591224128</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32693,28 +32961,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.03791948007635884</v>
+        <v>-0.05313973034617901</v>
       </c>
       <c r="J12" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K12" t="n">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0002896700661145779</v>
+        <v>0.0005768168189953515</v>
       </c>
       <c r="M12" t="n">
-        <v>12.42018205887464</v>
+        <v>12.37501685410423</v>
       </c>
       <c r="N12" t="n">
-        <v>219.932568538525</v>
+        <v>218.6155592293866</v>
       </c>
       <c r="O12" t="n">
-        <v>14.83012368588088</v>
+        <v>14.78565383165001</v>
       </c>
       <c r="P12" t="n">
-        <v>323.7986684822594</v>
+        <v>323.9962947759424</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32771,28 +33039,28 @@
         <v>0.1389</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3474560326950169</v>
+        <v>-0.3650466674760392</v>
       </c>
       <c r="J13" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K13" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L13" t="n">
-        <v>0.03216823542935454</v>
+        <v>0.03578678460488915</v>
       </c>
       <c r="M13" t="n">
-        <v>9.618482113759461</v>
+        <v>9.622750258994484</v>
       </c>
       <c r="N13" t="n">
-        <v>163.1383364540011</v>
+        <v>162.5638890729503</v>
       </c>
       <c r="O13" t="n">
-        <v>12.77256185947052</v>
+        <v>12.75005447333267</v>
       </c>
       <c r="P13" t="n">
-        <v>333.6905046131511</v>
+        <v>333.917486890066</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32849,28 +33117,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4287842659257428</v>
+        <v>-0.4331380964928245</v>
       </c>
       <c r="J14" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K14" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0478103774391212</v>
+        <v>0.04949368255897035</v>
       </c>
       <c r="M14" t="n">
-        <v>10.13599561586012</v>
+        <v>10.06977737367203</v>
       </c>
       <c r="N14" t="n">
-        <v>164.4608901117735</v>
+        <v>163.1304035254825</v>
       </c>
       <c r="O14" t="n">
-        <v>12.82423058556627</v>
+        <v>12.7722513099877</v>
       </c>
       <c r="P14" t="n">
-        <v>334.0108698352507</v>
+        <v>334.0671167941763</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32927,28 +33195,28 @@
         <v>0.089</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.24105291421048</v>
+        <v>-0.2546937875288604</v>
       </c>
       <c r="J15" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K15" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0251914842015899</v>
+        <v>0.02836237211541537</v>
       </c>
       <c r="M15" t="n">
-        <v>7.798586321355165</v>
+        <v>7.79063144222821</v>
       </c>
       <c r="N15" t="n">
-        <v>100.9889867384649</v>
+        <v>100.6179308540822</v>
       </c>
       <c r="O15" t="n">
-        <v>10.04932767594255</v>
+        <v>10.03084895978811</v>
       </c>
       <c r="P15" t="n">
-        <v>335.0346729352511</v>
+        <v>335.2106883314503</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33005,28 +33273,28 @@
         <v>0.035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3497933717828401</v>
+        <v>-0.3676839479508014</v>
       </c>
       <c r="J16" t="n">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="K16" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05248560106069156</v>
+        <v>0.05811517901859709</v>
       </c>
       <c r="M16" t="n">
-        <v>7.562616765861063</v>
+        <v>7.575501041640617</v>
       </c>
       <c r="N16" t="n">
-        <v>99.20932122645861</v>
+        <v>99.20520584643936</v>
       </c>
       <c r="O16" t="n">
-        <v>9.960387604227991</v>
+        <v>9.960181014742622</v>
       </c>
       <c r="P16" t="n">
-        <v>333.7844795214478</v>
+        <v>334.0153018696039</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33064,7 +33332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q456"/>
+  <dimension ref="A1:Q460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72607,6 +72875,354 @@
         </is>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>-45.89904360874076,170.6523242539984</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>-45.898248671183175,170.65207933867134</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>-45.89781893510702,170.6514222644005</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>-45.89746117165327,170.65065747780085</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>-45.89715671551049,170.64983979383294</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>-45.896946276706124,170.64897416716568</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-45.89681140447114,170.64808808240815</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-45.896477053208656,170.64728097275147</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>-45.89629677687695,170.6463847813161</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>-45.89626119310687,170.64547385822198</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>-45.89619995857166,170.64457809942317</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>-45.89612837857262,170.64368528717742</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>-45.89609431258567,170.64278892783807</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>-45.895961045456545,170.6419170669039</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>-45.89576835854488,170.64105877729756</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-04 22:20:37+00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>-45.89904714204898,170.65232026636636</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>-45.89824174589752,170.65208715431487</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>-45.8978137764979,170.65142808624978</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>-45.897454264768854,170.65066401053073</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>-45.897152703313864,170.6498424099955</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-45.89694256690559,170.64897614544</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-45.89680668292166,170.64809060025684</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>-45.89647618884704,170.6472813302474</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>-45.896296423125726,170.64638487597634</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>-45.896256754985195,170.645474909448</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>-45.896196496842194,170.64457891941643</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>-45.89611027627974,170.64368962123652</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>-45.89607374636291,170.64279473827366</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>-45.89595341061049,170.6419195369591</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>-45.89577195656896,170.64105761321568</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>-45.89904367940694,170.65232417424573</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>-45.898237293927885,170.65209217865612</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>-45.89780847655668,170.65143406760063</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>-45.89744983535364,170.65066819999794</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-45.89715041063007,170.64984390494539</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-45.89693826690943,170.64897843843937</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-45.89680339469965,170.6480923537584</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>-45.896474546559965,170.64728200948963</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>-45.896294212180706,170.64638546760273</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>-45.89625116295186,170.6454762339926</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>-45.89619294635044,170.64457976043505</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>-45.89609607840278,170.64369302049644</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>-45.89605379800908,170.64280037414244</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>-45.89594437165471,170.64192246127647</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>-45.8957670421946,170.64105920318116</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>-45.89904367940694,170.65232417424573</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>-45.898239060582526,170.65209018487002</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>-45.89781038453556,170.65143191431443</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>-45.89745118670066,170.65066692185547</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-45.89715090191945,170.64984358459895</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-45.89693911004594,170.64897798883166</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>-45.89680179274535,170.64809320802826</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>-45.89647402794301,170.64728222398713</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>-45.89629783813056,170.6463844973354</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>-45.89625045285239,170.64547640218873</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>-45.89618788689965,170.64458095888637</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>-45.89608853578057,170.64369482635252</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>-45.896034114456,170.64280593519456</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>-45.89593024280126,170.64192703229477</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>-45.895749754127436,170.64106479645017</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
